--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/ALASKA_2015.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/ALASKA_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C3">
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -638,7 +703,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Tepehuanes</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -778,7 +883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>León</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -897,7 +1032,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C38">
@@ -908,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C39">
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -952,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C42">
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Zempoala</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1009,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Cihuatlán</t>
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1061,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C50">
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1087,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Valle de Guadalupe</t>
+          <t>Valle De Guadalupe</t>
         </is>
       </c>
       <c r="C52">
@@ -1100,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zapotitlán de Vadillo</t>
+          <t>Zapotitlán De Vadillo</t>
         </is>
       </c>
       <c r="C53">
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1122,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>0.09316770186335403</v>
+        <v>0.09316770186335405</v>
       </c>
     </row>
     <row r="55">
@@ -1144,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -1157,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Ecuandureo</t>
@@ -1170,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -1183,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -1196,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1209,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -1222,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -1235,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1248,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1261,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1305,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -1318,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1349,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1362,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -1375,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1406,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1437,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C77">
@@ -1450,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C78">
@@ -1463,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C79">
@@ -1476,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C80">
@@ -1489,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>San Jacinto Tlacotepec</t>
@@ -1502,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>San Simón Almolongas</t>
@@ -1515,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Santa María Yucuhiti</t>
@@ -1528,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -1541,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C85">
@@ -1554,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1585,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Huehuetlán el Grande</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C88">
@@ -1598,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -1611,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -1624,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -1637,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -1650,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1670,7 +2040,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C94">
@@ -1681,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -1694,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1714,7 +2094,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C97">
@@ -1725,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1756,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>El Fuerte</t>
@@ -1769,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -1782,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -1795,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -1808,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -1821,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1852,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1883,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -1896,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1927,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -1940,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C113">
@@ -1953,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1984,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1997,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -2010,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -2023,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -2036,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C120">
@@ -2049,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -2062,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -2075,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2098,41 +2583,6 @@
       </c>
       <c r="D124">
         <v>1</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
